--- a/bloomberg/KRW_KevinGrid.xlsx
+++ b/bloomberg/KRW_KevinGrid.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DV01" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quotes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interpolation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amort-Set-up" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KRD" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quotes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interpolation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amort-Set-up" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KRD" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KRD reformed" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="0.00000000"/>
     <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +63,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
       <color rgb="00808080"/>
       <sz val="9"/>
     </font>
@@ -116,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,6 +144,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -503,261 +510,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Delta - bump each tenor 1bp</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>KRW IRS loan hedge, 10Y. Each row = NPV change for +1bp on that tenor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tenor</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>dv01</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2D</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>1W</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2M</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="B9" s="5">
-        <f>KRD!S$69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>6M</t>
-        </is>
-      </c>
-      <c r="B10" s="5">
-        <f>KRD!T$69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>9M</t>
-        </is>
-      </c>
-      <c r="B11" s="5">
-        <f>KRD!U$69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>1Y</t>
-        </is>
-      </c>
-      <c r="B12" s="5">
-        <f>KRD!V$69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2Y</t>
-        </is>
-      </c>
-      <c r="B13" s="5">
-        <f>KRD!W$69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="B14" s="5">
-        <f>KRD!X$69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>4Y</t>
-        </is>
-      </c>
-      <c r="B15" s="5">
-        <f>KRD!Y$69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="B16" s="5">
-        <f>KRD!Z$69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>7Y</t>
-        </is>
-      </c>
-      <c r="B17" s="5">
-        <f>KRD!AA$69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="B18" s="5">
-        <f>KRD!AB$69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>12Y</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>15Y</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>20Y</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>25Y</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>30Y</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B24" s="7">
-        <f>SUM(B5:B23)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -969,7 +721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2560,7 +2312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5241,7 +4993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6987,7 +6739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12488,4 +12240,274 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta — 1bp per tenor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>KRW IRS loan hedge, 10Y. Each row = change in NPV for +1bp on that tenor. Live off the KRD delta row — reprices when the notionals or curve change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tenor</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>dv01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2D</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>2D–2M: no curve node below 3M / no swap sensitivity → 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1W</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>12Y–30Y: past the 10Y maturity → 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>8Y/9Y risk sits in the 7Y and 10Y buckets (dropped as nodes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="B9" s="5">
+        <f>KRD!S$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="B10" s="5">
+        <f>KRD!T$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>KRD!U$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="B12" s="5">
+        <f>KRD!V$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="B13" s="5">
+        <f>KRD!W$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>KRD!X$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>4Y</t>
+        </is>
+      </c>
+      <c r="B15" s="5">
+        <f>KRD!Y$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="B16" s="5">
+        <f>KRD!Z$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>KRD!AA$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="B18" s="5">
+        <f>KRD!AB$69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>12Y</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>15Y</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>25Y</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B24" s="7">
+        <f>SUM(B5:B23)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>